--- a/Hoadon/HD2026/HDRa/3/3502551856_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDRa/3/3502551856_HDDienTuMayTinhTien.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>Hóa đơn mới</t>
+          <t>Hóa đơn đã bị thay thế</t>
         </is>
       </c>
       <c r="Q18" s="6" t="inlineStr">
@@ -2337,6 +2337,371 @@
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K35" s="6"/>
+      <c r="L35" s="13" t="n">
+        <v>9.2E7</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>9.2E7</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K36" s="6"/>
+      <c r="L36" s="13" t="n">
+        <v>1.32E7</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>1.32E7</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K37" s="6"/>
+      <c r="L37" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K38" s="6"/>
+      <c r="L38" s="13" t="n">
+        <v>8250000.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="13" t="n">
+        <v>8250000.0</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K39" s="6"/>
+      <c r="L39" s="13" t="n">
+        <v>1650000.0</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O39" s="13" t="n">
+        <v>1650000.0</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HD2026/HDRa/3/3502551856_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDRa/3/3502551856_HDDienTuMayTinhTien.xlsx
@@ -2707,6 +2707,3948 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K40" s="6"/>
+      <c r="L40" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O40" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K41" s="6"/>
+      <c r="L41" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O41" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K42" s="6"/>
+      <c r="L42" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O42" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O43" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K46" s="6"/>
+      <c r="L46" s="13" t="n">
+        <v>-4.1809523E7</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>-2090477.0</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>-4.39E7</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K47" s="6"/>
+      <c r="L47" s="13" t="n">
+        <v>-4.39E7</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O47" s="13" t="n">
+        <v>-4.39E7</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K48" s="6"/>
+      <c r="L48" s="13" t="n">
+        <v>4.39E7</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O48" s="13" t="n">
+        <v>4.39E7</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K49" s="6"/>
+      <c r="L49" s="13" t="n">
+        <v>-1571429.0</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>-78571.0</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O49" s="13" t="n">
+        <v>-1650000.0</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K50" s="6"/>
+      <c r="L50" s="13" t="n">
+        <v>-1650000.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O50" s="13" t="n">
+        <v>-1650000.0</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13" t="n">
+        <v>1650000.0</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O51" s="13" t="n">
+        <v>1650000.0</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K52" s="6"/>
+      <c r="L52" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O52" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K53" s="6"/>
+      <c r="L53" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K54" s="6"/>
+      <c r="L54" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K55" s="6"/>
+      <c r="L55" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O55" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K56" s="6"/>
+      <c r="L56" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O56" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K57" s="6"/>
+      <c r="L57" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K58" s="6"/>
+      <c r="L58" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O58" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K59" s="6"/>
+      <c r="L59" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K60" s="6"/>
+      <c r="L60" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O60" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K61" s="6"/>
+      <c r="L61" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K62" s="6"/>
+      <c r="L62" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K63" s="6"/>
+      <c r="L63" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K64" s="6"/>
+      <c r="L64" s="13" t="n">
+        <v>-6238095.0</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>-311905.0</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>-6550000.0</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K65" s="6"/>
+      <c r="L65" s="13" t="n">
+        <v>6550000.0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>6550000.0</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K66" s="6"/>
+      <c r="L66" s="13" t="n">
+        <v>-6550000.0</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>-6550000.0</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K67" s="6"/>
+      <c r="L67" s="13" t="n">
+        <v>-6550000.0</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>-6550000.0</v>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K68" s="6"/>
+      <c r="L68" s="13" t="n">
+        <v>6550000.0</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N68" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O68" s="13" t="n">
+        <v>6550000.0</v>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K69" s="6"/>
+      <c r="L69" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N69" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O69" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K70" s="6"/>
+      <c r="L70" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="M70" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N70" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O70" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K71" s="6"/>
+      <c r="L71" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N71" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K72" s="6"/>
+      <c r="L72" s="13" t="n">
+        <v>-2.2E7</v>
+      </c>
+      <c r="M72" s="13" t="n">
+        <v>-1100000.0</v>
+      </c>
+      <c r="N72" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O72" s="13" t="n">
+        <v>-2.31E7</v>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K73" s="6"/>
+      <c r="L73" s="13" t="n">
+        <v>-2.31E7</v>
+      </c>
+      <c r="M73" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N73" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>-2.31E7</v>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K74" s="6"/>
+      <c r="L74" s="13" t="n">
+        <v>2.31E7</v>
+      </c>
+      <c r="M74" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N74" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O74" s="13" t="n">
+        <v>2.31E7</v>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K75" s="6"/>
+      <c r="L75" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M75" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N75" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O75" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K76" s="6"/>
+      <c r="L76" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N76" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O76" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>71.0</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K77" s="6"/>
+      <c r="L77" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N77" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O77" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>72.0</v>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K78" s="6"/>
+      <c r="L78" s="13" t="n">
+        <v>-2180953.0</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>-109047.0</v>
+      </c>
+      <c r="N78" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O78" s="13" t="n">
+        <v>-2290000.0</v>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>73.0</v>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K79" s="6"/>
+      <c r="L79" s="13" t="n">
+        <v>-2290000.0</v>
+      </c>
+      <c r="M79" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N79" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O79" s="13" t="n">
+        <v>-2290000.0</v>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>74.0</v>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K80" s="6"/>
+      <c r="L80" s="13" t="n">
+        <v>2290000.0</v>
+      </c>
+      <c r="M80" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N80" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O80" s="13" t="n">
+        <v>2290000.0</v>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>75.0</v>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K81" s="6"/>
+      <c r="L81" s="13" t="n">
+        <v>1.1E7</v>
+      </c>
+      <c r="M81" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N81" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O81" s="13" t="n">
+        <v>1.1E7</v>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn thay thế</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>76.0</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K82" s="6"/>
+      <c r="L82" s="13" t="n">
+        <v>-1.047619E7</v>
+      </c>
+      <c r="M82" s="13" t="n">
+        <v>-523810.0</v>
+      </c>
+      <c r="N82" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O82" s="13" t="n">
+        <v>-1.1E7</v>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>77.0</v>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K83" s="6"/>
+      <c r="L83" s="13" t="n">
+        <v>1.1E7</v>
+      </c>
+      <c r="M83" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N83" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O83" s="13" t="n">
+        <v>1.1E7</v>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>78.0</v>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K84" s="6"/>
+      <c r="L84" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M84" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N84" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O84" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>79.0</v>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K85" s="6"/>
+      <c r="L85" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M85" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N85" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>80.0</v>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K86" s="6"/>
+      <c r="L86" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M86" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N86" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O86" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>81.0</v>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K87" s="6"/>
+      <c r="L87" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M87" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N87" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O87" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>82.0</v>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K88" s="6"/>
+      <c r="L88" s="13" t="n">
+        <v>-1.8857143E7</v>
+      </c>
+      <c r="M88" s="13" t="n">
+        <v>-942857.0</v>
+      </c>
+      <c r="N88" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O88" s="13" t="n">
+        <v>-1.98E7</v>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>83.0</v>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K89" s="6"/>
+      <c r="L89" s="13" t="n">
+        <v>1.98E7</v>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N89" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O89" s="13" t="n">
+        <v>1.98E7</v>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>84.0</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K90" s="6"/>
+      <c r="L90" s="13" t="n">
+        <v>-4689524.0</v>
+      </c>
+      <c r="M90" s="13" t="n">
+        <v>-234476.0</v>
+      </c>
+      <c r="N90" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O90" s="13" t="n">
+        <v>-4924000.0</v>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>85.0</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K91" s="6"/>
+      <c r="L91" s="13" t="n">
+        <v>4924000.0</v>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>4924000.0</v>
+      </c>
+      <c r="P91" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K92" s="6"/>
+      <c r="L92" s="13" t="n">
+        <v>-2.1904762E7</v>
+      </c>
+      <c r="M92" s="13" t="n">
+        <v>-1095238.0</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>-2.3E7</v>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q92" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>87.0</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>C26MLH</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>26/03/2026</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>3502551856</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH LÊ HƯƠNG VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>3500835690</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ TỔNG HỢP DẦU KHÍ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>Số 63 đường 30/4, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K93" s="6"/>
+      <c r="L93" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="M93" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N93" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O93" s="13" t="n">
+        <v>2.3E7</v>
+      </c>
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn điều chỉnh</t>
+        </is>
+      </c>
+      <c r="Q93" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
